--- a/public/template-transazioni-liquidita-en.xlsx
+++ b/public/template-transazioni-liquidita-en.xlsx
@@ -479,7 +479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>- Container: name of an existing container, or leave empty for "Direct".</v>
+        <v>- Container: name of an existing container, or leave empty.</v>
       </c>
     </row>
     <row r="11">

--- a/public/template-transazioni-liquidita-en.xlsx
+++ b/public/template-transazioni-liquidita-en.xlsx
@@ -424,7 +424,7 @@
         <v>Withheld tax</v>
       </c>
       <c r="F1" t="str">
-        <v>Container</v>
+        <v>Group</v>
       </c>
     </row>
     <row r="2">
@@ -479,7 +479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>- Container: name of an existing container, or leave empty.</v>
+        <v>- Group: name of an existing group, or leave empty.</v>
       </c>
     </row>
     <row r="11">
